--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92574297451</v>
+        <v>46157.93117397979</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93117397979</v>
+        <v>46157.93183255201</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93183255201</v>
+        <v>46157.93405588889</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93405588889</v>
+        <v>46157.93723666369</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93723666369</v>
+        <v>46158.28221437845</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28221437845</v>
+        <v>46158.29701833319</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29701833319</v>
+        <v>46158.29821167802</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29821167802</v>
+        <v>46158.33392487603</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33392487603</v>
+        <v>46158.368622446</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.368622446</v>
+        <v>46158.37293189621</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
